--- a/ZYQDManager/wwwroot/Templates/装箱单模板-生产.xlsx
+++ b/ZYQDManager/wwwroot/Templates/装箱单模板-生产.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.3.240\品质登记\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JC_Project\ZYQDManager\ZYQDManager\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,15 +14,12 @@
   <sheets>
     <sheet name="生产装箱单" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">生产装箱单!#REF!</definedName>
-  </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>美国  Power Shades 11111+22222  装箱单</t>
   </si>
@@ -109,6 +106,14 @@
   </si>
   <si>
     <t>*TOTAL</t>
+  </si>
+  <si>
+    <t>铭牌1类型</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>铭牌2类型</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -116,7 +121,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -289,13 +294,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -337,7 +342,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
@@ -632,7 +637,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.75" style="5" customWidth="1"/>
@@ -641,21 +646,21 @@
     <col min="5" max="5" width="28.75" style="5" customWidth="1"/>
     <col min="6" max="6" width="46" style="5" customWidth="1"/>
     <col min="7" max="7" width="31.125" style="5" customWidth="1"/>
-    <col min="8" max="9" width="40.75" style="5" customWidth="1"/>
-    <col min="10" max="10" width="27.375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="53.75" style="5" customWidth="1"/>
-    <col min="12" max="12" width="21.875" style="5" customWidth="1"/>
-    <col min="13" max="13" width="23.375" style="5" customWidth="1"/>
-    <col min="14" max="15" width="11.875" style="5" customWidth="1"/>
-    <col min="16" max="16" width="25.75" customWidth="1"/>
-    <col min="17" max="17" width="26.625" customWidth="1"/>
-    <col min="18" max="18" width="29.625" customWidth="1"/>
-    <col min="19" max="24" width="21.75" customWidth="1"/>
-    <col min="25" max="25" width="24" customWidth="1"/>
-    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="8" max="11" width="40.75" style="5" customWidth="1"/>
+    <col min="12" max="12" width="27.375" style="5" customWidth="1"/>
+    <col min="13" max="13" width="53.75" style="5" customWidth="1"/>
+    <col min="14" max="14" width="21.875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="23.375" style="5" customWidth="1"/>
+    <col min="16" max="17" width="11.875" style="5" customWidth="1"/>
+    <col min="18" max="18" width="25.75" customWidth="1"/>
+    <col min="19" max="19" width="26.625" customWidth="1"/>
+    <col min="20" max="20" width="29.625" customWidth="1"/>
+    <col min="21" max="26" width="21.75" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -684,8 +689,10 @@
       <c r="X1" s="22"/>
       <c r="Y1" s="22"/>
       <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
     </row>
-    <row r="2" spans="1:26" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -711,61 +718,67 @@
         <v>8</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="P2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="Q2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="V2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="16" t="s">
+      <c r="W2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="17" t="s">
+      <c r="X2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="17" t="s">
+      <c r="Y2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="18" t="s">
+      <c r="Z2" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="20" t="s">
+      <c r="AA2" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="21" t="s">
+      <c r="AB2" s="21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="3" customFormat="1" ht="200.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" s="3" customFormat="1" ht="200.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -778,26 +791,28 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
-      <c r="K3" s="11"/>
+      <c r="K3" s="10"/>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
+      <c r="O3" s="11"/>
       <c r="P3" s="10"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="19" t="s">
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
       <c r="U3" s="10"/>
       <c r="V3" s="10"/>
       <c r="W3" s="10"/>
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
       <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
     </row>
-    <row r="4" spans="1:26" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -811,29 +826,31 @@
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
-      <c r="L4" s="15"/>
+      <c r="L4" s="12"/>
       <c r="M4" s="12"/>
       <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
       <c r="R4" s="12"/>
       <c r="S4" s="12"/>
       <c r="T4" s="12"/>
       <c r="U4" s="12"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
       <c r="X4" s="15"/>
       <c r="Y4" s="15"/>
       <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.2" right="0.2" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="98" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="98" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>